--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N37_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.83692103558577</v>
+        <v>6.734918836880376</v>
       </c>
       <c r="D2" t="n">
-        <v>4.791075362577121</v>
+        <v>6.493185281385152</v>
       </c>
       <c r="E2" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F2" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.69601517448935</v>
+        <v>4.83692103558577</v>
       </c>
       <c r="D3" t="n">
-        <v>33.85136738002578</v>
+        <v>4.791075362577121</v>
       </c>
       <c r="E3" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F3" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.933302825685042</v>
+        <v>33.69601517448935</v>
       </c>
       <c r="D4" t="n">
-        <v>8.839348959554497</v>
+        <v>33.85136738002578</v>
       </c>
       <c r="E4" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F4" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.32418374066723</v>
+        <v>8.933302825685042</v>
       </c>
       <c r="D5" t="n">
-        <v>21.53688289177423</v>
+        <v>8.839348959554497</v>
       </c>
       <c r="E5" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F5" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.79895650158651</v>
+        <v>21.32418374066723</v>
       </c>
       <c r="D6" t="n">
-        <v>31.60648755046749</v>
+        <v>21.53688289177423</v>
       </c>
       <c r="E6" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F6" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.23830857085996</v>
+        <v>31.79895650158651</v>
       </c>
       <c r="D7" t="n">
-        <v>21.01352279785715</v>
+        <v>31.60648755046749</v>
       </c>
       <c r="E7" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F7" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.31467798349561</v>
+        <v>21.23830857085996</v>
       </c>
       <c r="D8" t="n">
-        <v>30.04909423440913</v>
+        <v>21.01352279785715</v>
       </c>
       <c r="E8" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F8" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.25319339264331</v>
+        <v>30.31467798349561</v>
       </c>
       <c r="D9" t="n">
-        <v>18.62495693241226</v>
+        <v>30.04909423440913</v>
       </c>
       <c r="E9" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F9" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.20155302721989</v>
+        <v>18.25319339264331</v>
       </c>
       <c r="D10" t="n">
-        <v>24.69755605544658</v>
+        <v>18.62495693241226</v>
       </c>
       <c r="E10" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F10" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.76758204977918</v>
+        <v>26.20155302721989</v>
       </c>
       <c r="D11" t="n">
-        <v>17.89942291880299</v>
+        <v>24.69755605544658</v>
       </c>
       <c r="E11" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F11" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.71605801534886</v>
+        <v>18.76758204977918</v>
       </c>
       <c r="D12" t="n">
-        <v>15.36699808132797</v>
+        <v>17.89942291880299</v>
       </c>
       <c r="E12" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F12" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.240247680456359</v>
+        <v>13.71605801534886</v>
       </c>
       <c r="D13" t="n">
-        <v>7.912412952985083</v>
+        <v>15.36699808132797</v>
       </c>
       <c r="E13" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F13" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.18374847725001</v>
+        <v>7.240247680456359</v>
       </c>
       <c r="D14" t="n">
-        <v>15.12715033720151</v>
+        <v>7.912412952985083</v>
       </c>
       <c r="E14" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F14" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.99927636641279</v>
+        <v>13.18374847725001</v>
       </c>
       <c r="D15" t="n">
-        <v>21.23793394775888</v>
+        <v>15.12715033720151</v>
       </c>
       <c r="E15" t="n">
-        <v>8.845919398445153</v>
+        <v>9.156708569756301</v>
       </c>
       <c r="F15" t="n">
-        <v>8.677851008130451</v>
+        <v>9.037324326021549</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,23 +928,55 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
+        <v>22.99927636641279</v>
+      </c>
+      <c r="D16" t="n">
+        <v>21.23793394775888</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.156708569756301</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.037324326021549</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W0029F0001T0006Z000C1N37.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
         <v>29.18104799743181</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>31.06396962637228</v>
       </c>
-      <c r="E16" t="n">
-        <v>8.845919398445153</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8.677851008130451</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>T7604</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E17" t="n">
+        <v>9.156708569756301</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.037324326021549</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.734918836880376</v>
+        <v>1.094424310993061</v>
       </c>
       <c r="D2" t="n">
-        <v>6.493185281385152</v>
+        <v>1.055142608225087</v>
       </c>
       <c r="E2" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F2" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.83692103558577</v>
+        <v>0.7859996682826876</v>
       </c>
       <c r="D3" t="n">
-        <v>4.791075362577121</v>
+        <v>0.7785497464187823</v>
       </c>
       <c r="E3" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F3" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.69601517448935</v>
+        <v>5.475602465854521</v>
       </c>
       <c r="D4" t="n">
-        <v>33.85136738002578</v>
+        <v>5.500847199254189</v>
       </c>
       <c r="E4" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F4" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.933302825685042</v>
+        <v>1.451661709173819</v>
       </c>
       <c r="D5" t="n">
-        <v>8.839348959554497</v>
+        <v>1.436394205927606</v>
       </c>
       <c r="E5" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F5" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.32418374066723</v>
+        <v>3.465179857858425</v>
       </c>
       <c r="D6" t="n">
-        <v>21.53688289177423</v>
+        <v>3.499743469913312</v>
       </c>
       <c r="E6" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F6" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.79895650158651</v>
+        <v>5.167330431507808</v>
       </c>
       <c r="D7" t="n">
-        <v>31.60648755046749</v>
+        <v>5.136054226950967</v>
       </c>
       <c r="E7" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F7" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.23830857085996</v>
+        <v>3.451225142764743</v>
       </c>
       <c r="D8" t="n">
-        <v>21.01352279785715</v>
+        <v>3.414697454651786</v>
       </c>
       <c r="E8" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F8" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.31467798349561</v>
+        <v>4.926135172318037</v>
       </c>
       <c r="D9" t="n">
-        <v>30.04909423440913</v>
+        <v>4.882977813091483</v>
       </c>
       <c r="E9" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F9" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.25319339264331</v>
+        <v>2.966143926304538</v>
       </c>
       <c r="D10" t="n">
-        <v>18.62495693241226</v>
+        <v>3.026555501516992</v>
       </c>
       <c r="E10" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F10" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.20155302721989</v>
+        <v>4.257752366923232</v>
       </c>
       <c r="D11" t="n">
-        <v>24.69755605544658</v>
+        <v>4.01335285901007</v>
       </c>
       <c r="E11" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F11" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.76758204977918</v>
+        <v>3.049732083089116</v>
       </c>
       <c r="D12" t="n">
-        <v>17.89942291880299</v>
+        <v>2.908656224305485</v>
       </c>
       <c r="E12" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F12" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.71605801534886</v>
+        <v>2.22885942749419</v>
       </c>
       <c r="D13" t="n">
-        <v>15.36699808132797</v>
+        <v>2.497137188215795</v>
       </c>
       <c r="E13" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F13" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.240247680456359</v>
+        <v>1.176540248074158</v>
       </c>
       <c r="D14" t="n">
-        <v>7.912412952985083</v>
+        <v>1.285767104860076</v>
       </c>
       <c r="E14" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F14" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.18374847725001</v>
+        <v>2.142359127553127</v>
       </c>
       <c r="D15" t="n">
-        <v>15.12715033720151</v>
+        <v>2.458161929795245</v>
       </c>
       <c r="E15" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F15" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.99927636641279</v>
+        <v>3.737382409542079</v>
       </c>
       <c r="D16" t="n">
-        <v>21.23793394775888</v>
+        <v>3.451164266510817</v>
       </c>
       <c r="E16" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F16" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.18104799743181</v>
+        <v>4.741920299582669</v>
       </c>
       <c r="D17" t="n">
-        <v>31.06396962637228</v>
+        <v>5.047895064285496</v>
       </c>
       <c r="E17" t="n">
-        <v>9.156708569756301</v>
+        <v>1.487965142585399</v>
       </c>
       <c r="F17" t="n">
-        <v>9.037324326021549</v>
+        <v>1.468565202978502</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
